--- a/ProbabilityAndStatistic/notes/anki_cards/Prob general_table.xlsx
+++ b/ProbabilityAndStatistic/notes/anki_cards/Prob general_table.xlsx
@@ -504,7 +504,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>1788372110387</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,7 +549,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>1788372110388</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,7 +594,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>1788372110389</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -633,7 +639,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>1788372110390</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,7 +684,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>1788372110391</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -719,7 +729,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1788372110392</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -762,7 +774,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>1788372110393</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -805,7 +819,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>1788372110394</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -848,7 +864,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1788372110395</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -891,7 +909,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>1788372110396</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,7 +954,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1788372110397</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -977,7 +999,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1788372110398</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1020,7 +1044,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1788372110399</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1063,7 +1089,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1788372110400</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1106,7 +1134,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1788372110401</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1149,7 +1179,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1788372110402</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1192,7 +1224,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1788372110403</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1235,7 +1269,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1788372110404</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1278,7 +1314,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1788372110405</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1321,7 +1359,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>1788372110406</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1364,7 +1404,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1788372110407</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1407,7 +1449,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1788372110408</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1450,7 +1494,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1788372110409</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1493,7 +1539,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1788372110410</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1536,7 +1584,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1788372110411</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1579,7 +1629,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1788372110412</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1622,7 +1674,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>1788372051445</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1665,7 +1719,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>1788372051446</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1708,7 +1764,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>1788372051447</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1751,7 +1809,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>1788372051448</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1794,7 +1854,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>1788372051449</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1837,7 +1899,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>1788372051450</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1880,7 +1944,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>1788372051451</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1923,7 +1989,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1788372051452</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1966,7 +2034,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1788372051453</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2009,7 +2079,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>1788372051454</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2052,7 +2124,9 @@
           <t>Inno_2course_1semester::ProbaStat</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1788372051455</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
